--- a/summary/yes/exposures_meta_analysis_urothelial_carcinoma_of_the_bladder_combined.xlsx
+++ b/summary/yes/exposures_meta_analysis_urothelial_carcinoma_of_the_bladder_combined.xlsx
@@ -23,13 +23,16 @@
     <numFmt numFmtId="164" formatCode="0.0"/>
     <numFmt numFmtId="165" formatCode="0.0000"/>
   </numFmts>
-  <fonts count="2">
+  <fonts count="3">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
       <color theme="1"/>
       <sz val="11"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <b val="1"/>
     </font>
     <font>
       <b val="1"/>
@@ -49,7 +52,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="1">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -57,13 +60,22 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin"/>
+      <right style="thin"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="3" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -452,57 +464,57 @@
   </cols>
   <sheetData>
     <row r="1" ht="30" customHeight="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" s="2" t="inlineStr">
         <is>
           <t>Exposure</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" s="2" t="inlineStr">
         <is>
           <t>number estimates</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" s="2" t="inlineStr">
         <is>
           <t>Pooled RR</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="D1" s="2" t="inlineStr">
         <is>
           <t>lower CI RR</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="E1" s="2" t="inlineStr">
         <is>
           <t>upper CI RR</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="F1" s="2" t="inlineStr">
         <is>
           <t>lower PI RR</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="G1" s="2" t="inlineStr">
         <is>
           <t>upper PI RR</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="H1" s="2" t="inlineStr">
         <is>
           <t>I^2 (%)</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="I1" s="2" t="inlineStr">
         <is>
           <t>eggers p-value</t>
         </is>
       </c>
-      <c r="J1" s="1" t="inlineStr">
+      <c r="J1" s="2" t="inlineStr">
         <is>
           <t>total N</t>
         </is>
       </c>
-      <c r="K1" s="1" t="inlineStr">
+      <c r="K1" s="2" t="inlineStr">
         <is>
           <t>total Cases</t>
         </is>
@@ -514,28 +526,28 @@
           <t>eicosapentaenoic_acid</t>
         </is>
       </c>
-      <c r="B2" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="C2" s="3" t="n">
+      <c r="B2" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="C2" s="4" t="n">
         <v>0.32</v>
       </c>
-      <c r="D2" s="3" t="n">
+      <c r="D2" s="4" t="n">
         <v>0.19</v>
       </c>
-      <c r="E2" s="3" t="n">
+      <c r="E2" s="4" t="n">
         <v>0.52</v>
       </c>
-      <c r="F2" s="3" t="inlineStr"/>
-      <c r="G2" s="3" t="inlineStr"/>
-      <c r="H2" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="I2" s="5" t="inlineStr"/>
-      <c r="J2" s="2" t="n">
+      <c r="F2" s="4" t="inlineStr"/>
+      <c r="G2" s="4" t="inlineStr"/>
+      <c r="H2" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="I2" s="6" t="inlineStr"/>
+      <c r="J2" s="3" t="n">
         <v>500</v>
       </c>
-      <c r="K2" s="2" t="n">
+      <c r="K2" s="3" t="n">
         <v>250</v>
       </c>
     </row>
@@ -545,28 +557,28 @@
           <t>omega_3_fatty_acids</t>
         </is>
       </c>
-      <c r="B3" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="C3" s="3" t="n">
+      <c r="B3" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="C3" s="4" t="n">
         <v>0.32</v>
       </c>
-      <c r="D3" s="3" t="n">
+      <c r="D3" s="4" t="n">
         <v>0.19</v>
       </c>
-      <c r="E3" s="3" t="n">
+      <c r="E3" s="4" t="n">
         <v>0.52</v>
       </c>
-      <c r="F3" s="3" t="inlineStr"/>
-      <c r="G3" s="3" t="inlineStr"/>
-      <c r="H3" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="I3" s="5" t="inlineStr"/>
-      <c r="J3" s="2" t="n">
+      <c r="F3" s="4" t="inlineStr"/>
+      <c r="G3" s="4" t="inlineStr"/>
+      <c r="H3" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="I3" s="6" t="inlineStr"/>
+      <c r="J3" s="3" t="n">
         <v>500</v>
       </c>
-      <c r="K3" s="2" t="n">
+      <c r="K3" s="3" t="n">
         <v>250</v>
       </c>
     </row>
@@ -576,28 +588,28 @@
           <t>docosahexaenoic_acid</t>
         </is>
       </c>
-      <c r="B4" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="C4" s="3" t="n">
+      <c r="B4" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="C4" s="4" t="n">
         <v>0.33</v>
       </c>
-      <c r="D4" s="3" t="n">
+      <c r="D4" s="4" t="n">
         <v>0.2</v>
       </c>
-      <c r="E4" s="3" t="n">
+      <c r="E4" s="4" t="n">
         <v>0.53</v>
       </c>
-      <c r="F4" s="3" t="inlineStr"/>
-      <c r="G4" s="3" t="inlineStr"/>
-      <c r="H4" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="I4" s="5" t="inlineStr"/>
-      <c r="J4" s="2" t="n">
+      <c r="F4" s="4" t="inlineStr"/>
+      <c r="G4" s="4" t="inlineStr"/>
+      <c r="H4" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="I4" s="6" t="inlineStr"/>
+      <c r="J4" s="3" t="n">
         <v>500</v>
       </c>
-      <c r="K4" s="2" t="n">
+      <c r="K4" s="3" t="n">
         <v>250</v>
       </c>
     </row>
@@ -607,28 +619,28 @@
           <t>vitamin_d</t>
         </is>
       </c>
-      <c r="B5" s="2" t="n">
+      <c r="B5" s="3" t="n">
         <v>2</v>
       </c>
-      <c r="C5" s="3" t="n">
+      <c r="C5" s="4" t="n">
         <v>0.42</v>
       </c>
-      <c r="D5" s="3" t="n">
+      <c r="D5" s="4" t="n">
         <v>0.21</v>
       </c>
-      <c r="E5" s="3" t="n">
+      <c r="E5" s="4" t="n">
         <v>0.82</v>
       </c>
-      <c r="F5" s="3" t="inlineStr"/>
-      <c r="G5" s="3" t="inlineStr"/>
-      <c r="H5" s="4" t="n">
+      <c r="F5" s="4" t="inlineStr"/>
+      <c r="G5" s="4" t="inlineStr"/>
+      <c r="H5" s="5" t="n">
         <v>61.4</v>
       </c>
-      <c r="I5" s="5" t="inlineStr"/>
-      <c r="J5" s="2" t="n">
+      <c r="I5" s="6" t="inlineStr"/>
+      <c r="J5" s="3" t="n">
         <v>2653</v>
       </c>
-      <c r="K5" s="2" t="n">
+      <c r="K5" s="3" t="n">
         <v>1375</v>
       </c>
     </row>
@@ -638,28 +650,28 @@
           <t>dihomo_gamma_linolenic_acid</t>
         </is>
       </c>
-      <c r="B6" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="C6" s="3" t="n">
+      <c r="B6" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="C6" s="4" t="n">
         <v>0.47</v>
       </c>
-      <c r="D6" s="3" t="n">
+      <c r="D6" s="4" t="n">
         <v>0.29</v>
       </c>
-      <c r="E6" s="3" t="n">
+      <c r="E6" s="4" t="n">
         <v>0.74</v>
       </c>
-      <c r="F6" s="3" t="inlineStr"/>
-      <c r="G6" s="3" t="inlineStr"/>
-      <c r="H6" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="I6" s="5" t="inlineStr"/>
-      <c r="J6" s="2" t="n">
+      <c r="F6" s="4" t="inlineStr"/>
+      <c r="G6" s="4" t="inlineStr"/>
+      <c r="H6" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="I6" s="6" t="inlineStr"/>
+      <c r="J6" s="3" t="n">
         <v>500</v>
       </c>
-      <c r="K6" s="2" t="n">
+      <c r="K6" s="3" t="n">
         <v>250</v>
       </c>
     </row>
@@ -669,28 +681,28 @@
           <t>omega_6_fatty_acids</t>
         </is>
       </c>
-      <c r="B7" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="C7" s="3" t="n">
+      <c r="B7" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="C7" s="4" t="n">
         <v>0.47</v>
       </c>
-      <c r="D7" s="3" t="n">
+      <c r="D7" s="4" t="n">
         <v>0.29</v>
       </c>
-      <c r="E7" s="3" t="n">
+      <c r="E7" s="4" t="n">
         <v>0.74</v>
       </c>
-      <c r="F7" s="3" t="inlineStr"/>
-      <c r="G7" s="3" t="inlineStr"/>
-      <c r="H7" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="I7" s="5" t="inlineStr"/>
-      <c r="J7" s="2" t="n">
+      <c r="F7" s="4" t="inlineStr"/>
+      <c r="G7" s="4" t="inlineStr"/>
+      <c r="H7" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="I7" s="6" t="inlineStr"/>
+      <c r="J7" s="3" t="n">
         <v>500</v>
       </c>
-      <c r="K7" s="2" t="n">
+      <c r="K7" s="3" t="n">
         <v>250</v>
       </c>
     </row>
@@ -700,28 +712,28 @@
           <t>polyunsaturated_fat_pufa</t>
         </is>
       </c>
-      <c r="B8" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="C8" s="3" t="n">
+      <c r="B8" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="C8" s="4" t="n">
         <v>0.47</v>
       </c>
-      <c r="D8" s="3" t="n">
+      <c r="D8" s="4" t="n">
         <v>0.29</v>
       </c>
-      <c r="E8" s="3" t="n">
+      <c r="E8" s="4" t="n">
         <v>0.74</v>
       </c>
-      <c r="F8" s="3" t="inlineStr"/>
-      <c r="G8" s="3" t="inlineStr"/>
-      <c r="H8" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="I8" s="5" t="inlineStr"/>
-      <c r="J8" s="2" t="n">
+      <c r="F8" s="4" t="inlineStr"/>
+      <c r="G8" s="4" t="inlineStr"/>
+      <c r="H8" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="I8" s="6" t="inlineStr"/>
+      <c r="J8" s="3" t="n">
         <v>500</v>
       </c>
-      <c r="K8" s="2" t="n">
+      <c r="K8" s="3" t="n">
         <v>250</v>
       </c>
     </row>
@@ -731,28 +743,28 @@
           <t>monounsaturated_fat_mufa</t>
         </is>
       </c>
-      <c r="B9" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="C9" s="3" t="n">
+      <c r="B9" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="C9" s="4" t="n">
         <v>0.54</v>
       </c>
-      <c r="D9" s="3" t="n">
+      <c r="D9" s="4" t="n">
         <v>0.34</v>
       </c>
-      <c r="E9" s="3" t="n">
+      <c r="E9" s="4" t="n">
         <v>0.86</v>
       </c>
-      <c r="F9" s="3" t="inlineStr"/>
-      <c r="G9" s="3" t="inlineStr"/>
-      <c r="H9" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="I9" s="5" t="inlineStr"/>
-      <c r="J9" s="2" t="n">
+      <c r="F9" s="4" t="inlineStr"/>
+      <c r="G9" s="4" t="inlineStr"/>
+      <c r="H9" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="I9" s="6" t="inlineStr"/>
+      <c r="J9" s="3" t="n">
         <v>500</v>
       </c>
-      <c r="K9" s="2" t="n">
+      <c r="K9" s="3" t="n">
         <v>250</v>
       </c>
     </row>
@@ -762,28 +774,28 @@
           <t>oleic_acid</t>
         </is>
       </c>
-      <c r="B10" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="C10" s="3" t="n">
+      <c r="B10" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="C10" s="4" t="n">
         <v>0.54</v>
       </c>
-      <c r="D10" s="3" t="n">
+      <c r="D10" s="4" t="n">
         <v>0.34</v>
       </c>
-      <c r="E10" s="3" t="n">
+      <c r="E10" s="4" t="n">
         <v>0.86</v>
       </c>
-      <c r="F10" s="3" t="inlineStr"/>
-      <c r="G10" s="3" t="inlineStr"/>
-      <c r="H10" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="I10" s="5" t="inlineStr"/>
-      <c r="J10" s="2" t="n">
+      <c r="F10" s="4" t="inlineStr"/>
+      <c r="G10" s="4" t="inlineStr"/>
+      <c r="H10" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="I10" s="6" t="inlineStr"/>
+      <c r="J10" s="3" t="n">
         <v>500</v>
       </c>
-      <c r="K10" s="2" t="n">
+      <c r="K10" s="3" t="n">
         <v>250</v>
       </c>
     </row>
@@ -793,28 +805,28 @@
           <t>omega_9_fatty_acids</t>
         </is>
       </c>
-      <c r="B11" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="C11" s="3" t="n">
+      <c r="B11" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="C11" s="4" t="n">
         <v>0.54</v>
       </c>
-      <c r="D11" s="3" t="n">
+      <c r="D11" s="4" t="n">
         <v>0.34</v>
       </c>
-      <c r="E11" s="3" t="n">
+      <c r="E11" s="4" t="n">
         <v>0.86</v>
       </c>
-      <c r="F11" s="3" t="inlineStr"/>
-      <c r="G11" s="3" t="inlineStr"/>
-      <c r="H11" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="I11" s="5" t="inlineStr"/>
-      <c r="J11" s="2" t="n">
+      <c r="F11" s="4" t="inlineStr"/>
+      <c r="G11" s="4" t="inlineStr"/>
+      <c r="H11" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="I11" s="6" t="inlineStr"/>
+      <c r="J11" s="3" t="n">
         <v>500</v>
       </c>
-      <c r="K11" s="2" t="n">
+      <c r="K11" s="3" t="n">
         <v>250</v>
       </c>
     </row>
@@ -824,28 +836,28 @@
           <t>processed_meat_intake</t>
         </is>
       </c>
-      <c r="B12" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="C12" s="3" t="n">
+      <c r="B12" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="C12" s="4" t="n">
         <v>1.1</v>
       </c>
-      <c r="D12" s="3" t="n">
+      <c r="D12" s="4" t="n">
         <v>0.86</v>
       </c>
-      <c r="E12" s="3" t="n">
+      <c r="E12" s="4" t="n">
         <v>1.39</v>
       </c>
-      <c r="F12" s="3" t="inlineStr"/>
-      <c r="G12" s="3" t="inlineStr"/>
-      <c r="H12" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="I12" s="5" t="inlineStr"/>
-      <c r="J12" s="2" t="n">
+      <c r="F12" s="4" t="inlineStr"/>
+      <c r="G12" s="4" t="inlineStr"/>
+      <c r="H12" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="I12" s="6" t="inlineStr"/>
+      <c r="J12" s="3" t="n">
         <v>300933</v>
       </c>
-      <c r="K12" s="2" t="n">
+      <c r="K12" s="3" t="n">
         <v>854</v>
       </c>
     </row>
@@ -855,28 +867,28 @@
           <t>red_meat</t>
         </is>
       </c>
-      <c r="B13" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="C13" s="3" t="n">
+      <c r="B13" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="C13" s="4" t="n">
         <v>1.22</v>
       </c>
-      <c r="D13" s="3" t="n">
+      <c r="D13" s="4" t="n">
         <v>0.96</v>
       </c>
-      <c r="E13" s="3" t="n">
+      <c r="E13" s="4" t="n">
         <v>1.53</v>
       </c>
-      <c r="F13" s="3" t="inlineStr"/>
-      <c r="G13" s="3" t="inlineStr"/>
-      <c r="H13" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="I13" s="5" t="inlineStr"/>
-      <c r="J13" s="2" t="n">
+      <c r="F13" s="4" t="inlineStr"/>
+      <c r="G13" s="4" t="inlineStr"/>
+      <c r="H13" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="I13" s="6" t="inlineStr"/>
+      <c r="J13" s="3" t="n">
         <v>300933</v>
       </c>
-      <c r="K13" s="2" t="n">
+      <c r="K13" s="3" t="n">
         <v>854</v>
       </c>
     </row>
@@ -886,28 +898,28 @@
           <t>tea</t>
         </is>
       </c>
-      <c r="B14" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="C14" s="3" t="n">
+      <c r="B14" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="C14" s="4" t="n">
         <v>2.24</v>
       </c>
-      <c r="D14" s="3" t="n">
+      <c r="D14" s="4" t="n">
         <v>1.49</v>
       </c>
-      <c r="E14" s="3" t="n">
+      <c r="E14" s="4" t="n">
         <v>3.25</v>
       </c>
-      <c r="F14" s="3" t="inlineStr"/>
-      <c r="G14" s="3" t="inlineStr"/>
-      <c r="H14" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="I14" s="5" t="inlineStr"/>
-      <c r="J14" s="2" t="n">
+      <c r="F14" s="4" t="inlineStr"/>
+      <c r="G14" s="4" t="inlineStr"/>
+      <c r="H14" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="I14" s="6" t="inlineStr"/>
+      <c r="J14" s="3" t="n">
         <v>756</v>
       </c>
-      <c r="K14" s="2" t="n">
+      <c r="K14" s="3" t="n">
         <v>255</v>
       </c>
     </row>

--- a/summary/yes/exposures_meta_analysis_urothelial_carcinoma_of_the_bladder_combined.xlsx
+++ b/summary/yes/exposures_meta_analysis_urothelial_carcinoma_of_the_bladder_combined.xlsx
@@ -23,16 +23,13 @@
     <numFmt numFmtId="164" formatCode="0.0"/>
     <numFmt numFmtId="165" formatCode="0.0000"/>
   </numFmts>
-  <fonts count="3">
+  <fonts count="2">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
       <color theme="1"/>
       <sz val="11"/>
       <scheme val="minor"/>
-    </font>
-    <font>
-      <b val="1"/>
     </font>
     <font>
       <b val="1"/>
@@ -52,7 +49,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="1">
     <border>
       <left/>
       <right/>
@@ -60,22 +57,13 @@
       <bottom/>
       <diagonal/>
     </border>
-    <border>
-      <left style="thin"/>
-      <right style="thin"/>
-      <top style="thin"/>
-      <bottom style="thin"/>
-    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="3" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -464,57 +452,57 @@
   </cols>
   <sheetData>
     <row r="1" ht="30" customHeight="1">
-      <c r="A1" s="2" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>Exposure</t>
         </is>
       </c>
-      <c r="B1" s="2" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>number estimates</t>
         </is>
       </c>
-      <c r="C1" s="2" t="inlineStr">
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t>Pooled RR</t>
         </is>
       </c>
-      <c r="D1" s="2" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>lower CI RR</t>
         </is>
       </c>
-      <c r="E1" s="2" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>upper CI RR</t>
         </is>
       </c>
-      <c r="F1" s="2" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>lower PI RR</t>
         </is>
       </c>
-      <c r="G1" s="2" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>upper PI RR</t>
         </is>
       </c>
-      <c r="H1" s="2" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>I^2 (%)</t>
         </is>
       </c>
-      <c r="I1" s="2" t="inlineStr">
+      <c r="I1" s="1" t="inlineStr">
         <is>
           <t>eggers p-value</t>
         </is>
       </c>
-      <c r="J1" s="2" t="inlineStr">
+      <c r="J1" s="1" t="inlineStr">
         <is>
           <t>total N</t>
         </is>
       </c>
-      <c r="K1" s="2" t="inlineStr">
+      <c r="K1" s="1" t="inlineStr">
         <is>
           <t>total Cases</t>
         </is>
@@ -526,28 +514,28 @@
           <t>eicosapentaenoic_acid</t>
         </is>
       </c>
-      <c r="B2" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="C2" s="4" t="n">
+      <c r="B2" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="C2" s="3" t="n">
         <v>0.32</v>
       </c>
-      <c r="D2" s="4" t="n">
+      <c r="D2" s="3" t="n">
         <v>0.19</v>
       </c>
-      <c r="E2" s="4" t="n">
+      <c r="E2" s="3" t="n">
         <v>0.52</v>
       </c>
-      <c r="F2" s="4" t="inlineStr"/>
-      <c r="G2" s="4" t="inlineStr"/>
-      <c r="H2" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="I2" s="6" t="inlineStr"/>
-      <c r="J2" s="3" t="n">
+      <c r="F2" s="3" t="inlineStr"/>
+      <c r="G2" s="3" t="inlineStr"/>
+      <c r="H2" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="I2" s="5" t="inlineStr"/>
+      <c r="J2" s="2" t="n">
         <v>500</v>
       </c>
-      <c r="K2" s="3" t="n">
+      <c r="K2" s="2" t="n">
         <v>250</v>
       </c>
     </row>
@@ -557,28 +545,28 @@
           <t>omega_3_fatty_acids</t>
         </is>
       </c>
-      <c r="B3" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="C3" s="4" t="n">
+      <c r="B3" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="C3" s="3" t="n">
         <v>0.32</v>
       </c>
-      <c r="D3" s="4" t="n">
+      <c r="D3" s="3" t="n">
         <v>0.19</v>
       </c>
-      <c r="E3" s="4" t="n">
+      <c r="E3" s="3" t="n">
         <v>0.52</v>
       </c>
-      <c r="F3" s="4" t="inlineStr"/>
-      <c r="G3" s="4" t="inlineStr"/>
-      <c r="H3" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="I3" s="6" t="inlineStr"/>
-      <c r="J3" s="3" t="n">
+      <c r="F3" s="3" t="inlineStr"/>
+      <c r="G3" s="3" t="inlineStr"/>
+      <c r="H3" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="I3" s="5" t="inlineStr"/>
+      <c r="J3" s="2" t="n">
         <v>500</v>
       </c>
-      <c r="K3" s="3" t="n">
+      <c r="K3" s="2" t="n">
         <v>250</v>
       </c>
     </row>
@@ -588,28 +576,28 @@
           <t>docosahexaenoic_acid</t>
         </is>
       </c>
-      <c r="B4" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="C4" s="4" t="n">
+      <c r="B4" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="C4" s="3" t="n">
         <v>0.33</v>
       </c>
-      <c r="D4" s="4" t="n">
+      <c r="D4" s="3" t="n">
         <v>0.2</v>
       </c>
-      <c r="E4" s="4" t="n">
+      <c r="E4" s="3" t="n">
         <v>0.53</v>
       </c>
-      <c r="F4" s="4" t="inlineStr"/>
-      <c r="G4" s="4" t="inlineStr"/>
-      <c r="H4" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="I4" s="6" t="inlineStr"/>
-      <c r="J4" s="3" t="n">
+      <c r="F4" s="3" t="inlineStr"/>
+      <c r="G4" s="3" t="inlineStr"/>
+      <c r="H4" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="I4" s="5" t="inlineStr"/>
+      <c r="J4" s="2" t="n">
         <v>500</v>
       </c>
-      <c r="K4" s="3" t="n">
+      <c r="K4" s="2" t="n">
         <v>250</v>
       </c>
     </row>
@@ -619,28 +607,28 @@
           <t>vitamin_d</t>
         </is>
       </c>
-      <c r="B5" s="3" t="n">
+      <c r="B5" s="2" t="n">
         <v>2</v>
       </c>
-      <c r="C5" s="4" t="n">
+      <c r="C5" s="3" t="n">
         <v>0.42</v>
       </c>
-      <c r="D5" s="4" t="n">
+      <c r="D5" s="3" t="n">
         <v>0.21</v>
       </c>
-      <c r="E5" s="4" t="n">
+      <c r="E5" s="3" t="n">
         <v>0.82</v>
       </c>
-      <c r="F5" s="4" t="inlineStr"/>
-      <c r="G5" s="4" t="inlineStr"/>
-      <c r="H5" s="5" t="n">
+      <c r="F5" s="3" t="inlineStr"/>
+      <c r="G5" s="3" t="inlineStr"/>
+      <c r="H5" s="4" t="n">
         <v>61.4</v>
       </c>
-      <c r="I5" s="6" t="inlineStr"/>
-      <c r="J5" s="3" t="n">
+      <c r="I5" s="5" t="inlineStr"/>
+      <c r="J5" s="2" t="n">
         <v>2653</v>
       </c>
-      <c r="K5" s="3" t="n">
+      <c r="K5" s="2" t="n">
         <v>1375</v>
       </c>
     </row>
@@ -650,28 +638,28 @@
           <t>dihomo_gamma_linolenic_acid</t>
         </is>
       </c>
-      <c r="B6" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="C6" s="4" t="n">
+      <c r="B6" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="C6" s="3" t="n">
         <v>0.47</v>
       </c>
-      <c r="D6" s="4" t="n">
+      <c r="D6" s="3" t="n">
         <v>0.29</v>
       </c>
-      <c r="E6" s="4" t="n">
+      <c r="E6" s="3" t="n">
         <v>0.74</v>
       </c>
-      <c r="F6" s="4" t="inlineStr"/>
-      <c r="G6" s="4" t="inlineStr"/>
-      <c r="H6" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="I6" s="6" t="inlineStr"/>
-      <c r="J6" s="3" t="n">
+      <c r="F6" s="3" t="inlineStr"/>
+      <c r="G6" s="3" t="inlineStr"/>
+      <c r="H6" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="I6" s="5" t="inlineStr"/>
+      <c r="J6" s="2" t="n">
         <v>500</v>
       </c>
-      <c r="K6" s="3" t="n">
+      <c r="K6" s="2" t="n">
         <v>250</v>
       </c>
     </row>
@@ -681,28 +669,28 @@
           <t>omega_6_fatty_acids</t>
         </is>
       </c>
-      <c r="B7" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="C7" s="4" t="n">
+      <c r="B7" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="C7" s="3" t="n">
         <v>0.47</v>
       </c>
-      <c r="D7" s="4" t="n">
+      <c r="D7" s="3" t="n">
         <v>0.29</v>
       </c>
-      <c r="E7" s="4" t="n">
+      <c r="E7" s="3" t="n">
         <v>0.74</v>
       </c>
-      <c r="F7" s="4" t="inlineStr"/>
-      <c r="G7" s="4" t="inlineStr"/>
-      <c r="H7" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="I7" s="6" t="inlineStr"/>
-      <c r="J7" s="3" t="n">
+      <c r="F7" s="3" t="inlineStr"/>
+      <c r="G7" s="3" t="inlineStr"/>
+      <c r="H7" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="I7" s="5" t="inlineStr"/>
+      <c r="J7" s="2" t="n">
         <v>500</v>
       </c>
-      <c r="K7" s="3" t="n">
+      <c r="K7" s="2" t="n">
         <v>250</v>
       </c>
     </row>
@@ -712,28 +700,28 @@
           <t>polyunsaturated_fat_pufa</t>
         </is>
       </c>
-      <c r="B8" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="C8" s="4" t="n">
+      <c r="B8" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="C8" s="3" t="n">
         <v>0.47</v>
       </c>
-      <c r="D8" s="4" t="n">
+      <c r="D8" s="3" t="n">
         <v>0.29</v>
       </c>
-      <c r="E8" s="4" t="n">
+      <c r="E8" s="3" t="n">
         <v>0.74</v>
       </c>
-      <c r="F8" s="4" t="inlineStr"/>
-      <c r="G8" s="4" t="inlineStr"/>
-      <c r="H8" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="I8" s="6" t="inlineStr"/>
-      <c r="J8" s="3" t="n">
+      <c r="F8" s="3" t="inlineStr"/>
+      <c r="G8" s="3" t="inlineStr"/>
+      <c r="H8" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="I8" s="5" t="inlineStr"/>
+      <c r="J8" s="2" t="n">
         <v>500</v>
       </c>
-      <c r="K8" s="3" t="n">
+      <c r="K8" s="2" t="n">
         <v>250</v>
       </c>
     </row>
@@ -743,28 +731,28 @@
           <t>monounsaturated_fat_mufa</t>
         </is>
       </c>
-      <c r="B9" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="C9" s="4" t="n">
+      <c r="B9" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="C9" s="3" t="n">
         <v>0.54</v>
       </c>
-      <c r="D9" s="4" t="n">
+      <c r="D9" s="3" t="n">
         <v>0.34</v>
       </c>
-      <c r="E9" s="4" t="n">
+      <c r="E9" s="3" t="n">
         <v>0.86</v>
       </c>
-      <c r="F9" s="4" t="inlineStr"/>
-      <c r="G9" s="4" t="inlineStr"/>
-      <c r="H9" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="I9" s="6" t="inlineStr"/>
-      <c r="J9" s="3" t="n">
+      <c r="F9" s="3" t="inlineStr"/>
+      <c r="G9" s="3" t="inlineStr"/>
+      <c r="H9" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="I9" s="5" t="inlineStr"/>
+      <c r="J9" s="2" t="n">
         <v>500</v>
       </c>
-      <c r="K9" s="3" t="n">
+      <c r="K9" s="2" t="n">
         <v>250</v>
       </c>
     </row>
@@ -774,28 +762,28 @@
           <t>oleic_acid</t>
         </is>
       </c>
-      <c r="B10" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="C10" s="4" t="n">
+      <c r="B10" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="C10" s="3" t="n">
         <v>0.54</v>
       </c>
-      <c r="D10" s="4" t="n">
+      <c r="D10" s="3" t="n">
         <v>0.34</v>
       </c>
-      <c r="E10" s="4" t="n">
+      <c r="E10" s="3" t="n">
         <v>0.86</v>
       </c>
-      <c r="F10" s="4" t="inlineStr"/>
-      <c r="G10" s="4" t="inlineStr"/>
-      <c r="H10" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="I10" s="6" t="inlineStr"/>
-      <c r="J10" s="3" t="n">
+      <c r="F10" s="3" t="inlineStr"/>
+      <c r="G10" s="3" t="inlineStr"/>
+      <c r="H10" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="I10" s="5" t="inlineStr"/>
+      <c r="J10" s="2" t="n">
         <v>500</v>
       </c>
-      <c r="K10" s="3" t="n">
+      <c r="K10" s="2" t="n">
         <v>250</v>
       </c>
     </row>
@@ -805,28 +793,28 @@
           <t>omega_9_fatty_acids</t>
         </is>
       </c>
-      <c r="B11" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="C11" s="4" t="n">
+      <c r="B11" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="C11" s="3" t="n">
         <v>0.54</v>
       </c>
-      <c r="D11" s="4" t="n">
+      <c r="D11" s="3" t="n">
         <v>0.34</v>
       </c>
-      <c r="E11" s="4" t="n">
+      <c r="E11" s="3" t="n">
         <v>0.86</v>
       </c>
-      <c r="F11" s="4" t="inlineStr"/>
-      <c r="G11" s="4" t="inlineStr"/>
-      <c r="H11" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="I11" s="6" t="inlineStr"/>
-      <c r="J11" s="3" t="n">
+      <c r="F11" s="3" t="inlineStr"/>
+      <c r="G11" s="3" t="inlineStr"/>
+      <c r="H11" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="I11" s="5" t="inlineStr"/>
+      <c r="J11" s="2" t="n">
         <v>500</v>
       </c>
-      <c r="K11" s="3" t="n">
+      <c r="K11" s="2" t="n">
         <v>250</v>
       </c>
     </row>
@@ -836,28 +824,28 @@
           <t>processed_meat_intake</t>
         </is>
       </c>
-      <c r="B12" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="C12" s="4" t="n">
+      <c r="B12" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="C12" s="3" t="n">
         <v>1.1</v>
       </c>
-      <c r="D12" s="4" t="n">
+      <c r="D12" s="3" t="n">
         <v>0.86</v>
       </c>
-      <c r="E12" s="4" t="n">
+      <c r="E12" s="3" t="n">
         <v>1.39</v>
       </c>
-      <c r="F12" s="4" t="inlineStr"/>
-      <c r="G12" s="4" t="inlineStr"/>
-      <c r="H12" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="I12" s="6" t="inlineStr"/>
-      <c r="J12" s="3" t="n">
+      <c r="F12" s="3" t="inlineStr"/>
+      <c r="G12" s="3" t="inlineStr"/>
+      <c r="H12" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="I12" s="5" t="inlineStr"/>
+      <c r="J12" s="2" t="n">
         <v>300933</v>
       </c>
-      <c r="K12" s="3" t="n">
+      <c r="K12" s="2" t="n">
         <v>854</v>
       </c>
     </row>
@@ -867,28 +855,28 @@
           <t>red_meat</t>
         </is>
       </c>
-      <c r="B13" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="C13" s="4" t="n">
+      <c r="B13" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="C13" s="3" t="n">
         <v>1.22</v>
       </c>
-      <c r="D13" s="4" t="n">
+      <c r="D13" s="3" t="n">
         <v>0.96</v>
       </c>
-      <c r="E13" s="4" t="n">
+      <c r="E13" s="3" t="n">
         <v>1.53</v>
       </c>
-      <c r="F13" s="4" t="inlineStr"/>
-      <c r="G13" s="4" t="inlineStr"/>
-      <c r="H13" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="I13" s="6" t="inlineStr"/>
-      <c r="J13" s="3" t="n">
+      <c r="F13" s="3" t="inlineStr"/>
+      <c r="G13" s="3" t="inlineStr"/>
+      <c r="H13" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="I13" s="5" t="inlineStr"/>
+      <c r="J13" s="2" t="n">
         <v>300933</v>
       </c>
-      <c r="K13" s="3" t="n">
+      <c r="K13" s="2" t="n">
         <v>854</v>
       </c>
     </row>
@@ -898,28 +886,28 @@
           <t>tea</t>
         </is>
       </c>
-      <c r="B14" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="C14" s="4" t="n">
+      <c r="B14" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="C14" s="3" t="n">
         <v>2.24</v>
       </c>
-      <c r="D14" s="4" t="n">
+      <c r="D14" s="3" t="n">
         <v>1.49</v>
       </c>
-      <c r="E14" s="4" t="n">
+      <c r="E14" s="3" t="n">
         <v>3.25</v>
       </c>
-      <c r="F14" s="4" t="inlineStr"/>
-      <c r="G14" s="4" t="inlineStr"/>
-      <c r="H14" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="I14" s="6" t="inlineStr"/>
-      <c r="J14" s="3" t="n">
+      <c r="F14" s="3" t="inlineStr"/>
+      <c r="G14" s="3" t="inlineStr"/>
+      <c r="H14" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="I14" s="5" t="inlineStr"/>
+      <c r="J14" s="2" t="n">
         <v>756</v>
       </c>
-      <c r="K14" s="3" t="n">
+      <c r="K14" s="2" t="n">
         <v>255</v>
       </c>
     </row>
